--- a/data/Ledger 25.xlsx
+++ b/data/Ledger 25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dannelson/Desktop/we-serve/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8C5485-E00C-1B44-B4FC-A2161F6AEB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB670425-FDB2-4A43-AC87-C3E469F8338E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="1840" windowWidth="27240" windowHeight="16440" xr2:uid="{254E1F4E-7E9E-BF4D-B5B5-C1B5F03758AB}"/>
+    <workbookView xWindow="15380" yWindow="2540" windowWidth="22200" windowHeight="16440" xr2:uid="{254E1F4E-7E9E-BF4D-B5B5-C1B5F03758AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Ledger 24-25" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="58">
   <si>
     <t>Joyce Stevens</t>
   </si>
@@ -212,7 +212,10 @@
     <t>staff card</t>
   </si>
   <si>
-    <t>tbd</t>
+    <t>Liberty Mutual Ins</t>
+  </si>
+  <si>
+    <t>transfer</t>
   </si>
 </sst>
 </file>
@@ -428,7 +431,7 @@
             <v>75</v>
           </cell>
           <cell r="B15" t="str">
-            <v>Breakfast May-June 2026_inc</v>
+            <v>Breakfast May-June 2025_inc</v>
           </cell>
         </row>
         <row r="16">
@@ -1218,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAF488C-D52C-7F4A-B8B3-E5790FCBF255}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1273,9 +1276,9 @@
       <c r="D2" s="2">
         <v>4223</v>
       </c>
-      <c r="E2" s="2">
-        <f t="shared" ref="E2:E33" si="0">IF(D2=$J$1, 1, 0)</f>
-        <v>0</v>
+      <c r="E2" s="2" t="str">
+        <f>IF(D2=$J$1, "DEP","EXP")</f>
+        <v>EXP</v>
       </c>
       <c r="F2" s="3">
         <v>10.86</v>
@@ -1290,7 +1293,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f t="shared" ref="A3:A34" si="1">A2+1</f>
+        <f t="shared" ref="A3:A38" si="0">A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="10">
@@ -1302,9 +1305,9 @@
       <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E66" si="1">IF(D3=$J$1, "DEP","EXP")</f>
+        <v>DEP</v>
       </c>
       <c r="F3" s="3">
         <v>59.88</v>
@@ -1319,7 +1322,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="8">
@@ -1331,9 +1334,9 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F4" s="3">
         <v>1256.93</v>
@@ -1348,7 +1351,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="8">
@@ -1360,9 +1363,9 @@
       <c r="D5" s="2">
         <v>4224</v>
       </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F5" s="3">
         <v>327.95</v>
@@ -1377,7 +1380,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="8">
@@ -1389,9 +1392,9 @@
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F6" s="3">
         <v>587.75</v>
@@ -1406,7 +1409,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="8">
@@ -1418,9 +1421,9 @@
       <c r="D7" s="2">
         <v>4225</v>
       </c>
-      <c r="E7" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F7" s="3">
         <v>142.80000000000001</v>
@@ -1435,7 +1438,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="8">
@@ -1447,9 +1450,9 @@
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F8" s="3">
         <v>1765</v>
@@ -1464,7 +1467,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="8">
@@ -1476,9 +1479,9 @@
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F9" s="3">
         <v>0.28999999999999998</v>
@@ -1493,7 +1496,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="8">
@@ -1505,9 +1508,9 @@
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F10" s="3">
         <v>1644.75</v>
@@ -1522,7 +1525,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="8">
@@ -1534,9 +1537,9 @@
       <c r="D11" s="2">
         <v>4226</v>
       </c>
-      <c r="E11" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F11" s="3">
         <v>207.23</v>
@@ -1551,7 +1554,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="8">
@@ -1563,9 +1566,9 @@
       <c r="D12" s="2">
         <v>4228</v>
       </c>
-      <c r="E12" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F12" s="3">
         <v>1000</v>
@@ -1580,7 +1583,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="8">
@@ -1592,9 +1595,9 @@
       <c r="D13" s="2">
         <v>4227</v>
       </c>
-      <c r="E13" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F13" s="3">
         <v>128.53</v>
@@ -1609,7 +1612,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="8">
@@ -1621,9 +1624,9 @@
       <c r="D14" s="2">
         <v>4229</v>
       </c>
-      <c r="E14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F14" s="3">
         <v>1000</v>
@@ -1638,7 +1641,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="8">
@@ -1650,9 +1653,9 @@
       <c r="D15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F15" s="3">
         <v>604</v>
@@ -1667,7 +1670,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="8">
@@ -1679,9 +1682,9 @@
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F16" s="3">
         <v>1763</v>
@@ -1696,7 +1699,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="8">
@@ -1708,9 +1711,9 @@
       <c r="D17" s="2">
         <v>4230</v>
       </c>
-      <c r="E17" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F17" s="3">
         <v>48</v>
@@ -1725,7 +1728,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="8">
@@ -1737,9 +1740,9 @@
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F18" s="3">
         <v>0.33</v>
@@ -1754,7 +1757,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="8">
@@ -1766,9 +1769,9 @@
       <c r="D19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F19" s="3">
         <v>931</v>
@@ -1783,7 +1786,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="8">
@@ -1795,9 +1798,9 @@
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F20" s="3">
         <v>105</v>
@@ -1812,7 +1815,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="8">
@@ -1824,9 +1827,9 @@
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F21" s="3">
         <v>1000</v>
@@ -1841,7 +1844,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="8">
@@ -1853,9 +1856,9 @@
       <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F22" s="3">
         <f>1180.7-95</f>
@@ -1871,7 +1874,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="8">
@@ -1883,9 +1886,9 @@
       <c r="D23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F23" s="3">
         <v>95</v>
@@ -1900,7 +1903,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="8">
@@ -1912,9 +1915,9 @@
       <c r="D24" s="2">
         <v>4233</v>
       </c>
-      <c r="E24" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F24" s="3">
         <v>7.98</v>
@@ -1929,7 +1932,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="8">
@@ -1941,9 +1944,9 @@
       <c r="D25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F25" s="3">
         <v>395.44</v>
@@ -1958,7 +1961,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="8">
@@ -1970,9 +1973,9 @@
       <c r="D26" s="2">
         <v>4231</v>
       </c>
-      <c r="E26" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E26" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F26" s="3">
         <v>59.63</v>
@@ -1987,7 +1990,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="8">
@@ -1999,9 +2002,9 @@
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E27" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F27" s="3">
         <v>900</v>
@@ -2016,7 +2019,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="8">
@@ -2028,9 +2031,9 @@
       <c r="D28" s="2">
         <v>4232</v>
       </c>
-      <c r="E28" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E28" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F28" s="3">
         <v>1000</v>
@@ -2045,7 +2048,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="8">
@@ -2057,9 +2060,9 @@
       <c r="D29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E29" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F29" s="3">
         <v>0.28000000000000003</v>
@@ -2074,7 +2077,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
-        <f t="shared" si="1"/>
+        <f>A29+1</f>
         <v>29</v>
       </c>
       <c r="B30" s="8">
@@ -2086,9 +2089,9 @@
       <c r="D30" s="2">
         <v>4235</v>
       </c>
-      <c r="E30" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E30" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F30" s="3">
         <v>55</v>
@@ -2103,7 +2106,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="8">
@@ -2115,9 +2118,9 @@
       <c r="D31" s="2">
         <v>4234</v>
       </c>
-      <c r="E31" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="E31" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F31" s="3">
         <v>636.55999999999995</v>
@@ -2132,7 +2135,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="8">
@@ -2144,9 +2147,9 @@
       <c r="D32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E32" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F32" s="3">
         <v>300</v>
@@ -2161,7 +2164,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="8">
@@ -2173,9 +2176,9 @@
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="2">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="E33" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F33" s="3">
         <v>2665</v>
@@ -2190,616 +2193,616 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="8">
-        <v>45576</v>
+        <v>45600</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="D34" s="2">
-        <v>4239</v>
-      </c>
-      <c r="E34" s="2">
-        <f t="shared" ref="E34:E65" si="2">IF(D34=$J$1, 1, 0)</f>
-        <v>0</v>
+        <v>3146</v>
+      </c>
+      <c r="E34" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F34" s="3">
-        <v>1328</v>
+        <v>425</v>
       </c>
       <c r="G34" s="9">
-        <v>30</v>
+        <v>220</v>
       </c>
       <c r="H34" s="6" t="str">
         <f>VLOOKUP(G34,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>AmbassadorSummer</v>
+        <v>InsuranceOnBuildingContents</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
-        <f t="shared" ref="A35:A66" si="3">A34+1</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="8">
-        <v>45580</v>
+        <v>45576</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D35" s="2">
-        <v>4236</v>
-      </c>
-      <c r="E35" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4239</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F35" s="3">
-        <v>137.5</v>
+        <v>1328</v>
       </c>
       <c r="G35" s="9">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="H35" s="6" t="str">
         <f>VLOOKUP(G35,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>EyeGlasses &amp; HearingAids</v>
+        <v>AmbassadorSummer</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="8">
-        <v>45582</v>
+        <v>45580</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2">
-        <v>4238</v>
-      </c>
-      <c r="E36" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4236</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F36" s="3">
-        <v>92.98</v>
+        <v>137.5</v>
       </c>
       <c r="G36" s="9">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="H36" s="6" t="str">
         <f>VLOOKUP(G36,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Breakfast Jul-Sept 2024</v>
+        <v>EyeGlasses &amp; HearingAids</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="8">
-        <v>45589</v>
+        <v>45582</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D37" s="2">
-        <v>4237</v>
-      </c>
-      <c r="E37" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4238</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F37" s="3">
-        <v>295</v>
+        <v>92.98</v>
       </c>
       <c r="G37" s="9">
-        <v>330</v>
+        <v>60</v>
       </c>
       <c r="H37" s="6" t="str">
         <f>VLOOKUP(G37,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>VisionScreening</v>
+        <v>Breakfast Jul-Sept 2024</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="8">
-        <v>45595</v>
+        <v>45589</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D38" s="2">
-        <v>0</v>
-      </c>
-      <c r="E38" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4237</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F38" s="3">
-        <v>177.79</v>
+        <v>295</v>
       </c>
       <c r="G38" s="9">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="H38" s="6" t="str">
         <f>VLOOKUP(G38,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport</v>
+        <v>VisionScreening</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A36:A67" si="2">A38+1</f>
         <v>38</v>
       </c>
       <c r="B39" s="8">
-        <v>45596</v>
+        <v>45595</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F39" s="3">
-        <v>0.34</v>
+        <v>177.79</v>
       </c>
       <c r="G39" s="9">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="H39" s="6" t="str">
         <f>VLOOKUP(G39,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>InterestOnBankAccounts_inc</v>
+        <v>MiscCommunitySupport</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="B40" s="8">
-        <v>45600</v>
+        <v>45596</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D40" s="2">
-        <v>4240</v>
-      </c>
-      <c r="E40" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F40" s="3">
-        <v>2000</v>
+        <v>0.34</v>
       </c>
       <c r="G40" s="9">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="H40" s="6" t="str">
         <f>VLOOKUP(G40,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>LCIF</v>
+        <v>InterestOnBankAccounts_inc</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="B41" s="8">
-        <v>45621</v>
+        <v>45600</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="D41" s="2">
+        <v>4240</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F41" s="3">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="G41" s="9">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="H41" s="6" t="str">
         <f>VLOOKUP(G41,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Clothing4Kids_inc</v>
+        <v>LCIF</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="B42" s="8">
-        <v>45622</v>
+        <v>45621</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" s="2">
-        <v>4243</v>
-      </c>
-      <c r="E42" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F42" s="3">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="G42" s="9">
-        <v>260</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="str">
         <f>VLOOKUP(G42,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MEND</v>
+        <v>Clothing4Kids_inc</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="B43" s="8">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D43" s="2">
-        <v>4242</v>
-      </c>
-      <c r="E43" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4243</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F43" s="3">
-        <v>111.19</v>
+        <v>500</v>
       </c>
       <c r="G43" s="9">
-        <v>150</v>
+        <v>260</v>
       </c>
       <c r="H43" s="6" t="str">
         <f>VLOOKUP(G43,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Clothing4Kids</v>
+        <v>MEND</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>43</v>
       </c>
       <c r="B44" s="8">
-        <v>45627</v>
+        <v>45623</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="D44" s="2">
+        <v>4242</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F44" s="3">
-        <v>0.33</v>
+        <v>111.19</v>
       </c>
       <c r="G44" s="9">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="H44" s="6" t="str">
         <f>VLOOKUP(G44,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>InterestOnBankAccounts_inc</v>
+        <v>Clothing4Kids</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>44</v>
       </c>
       <c r="B45" s="8">
-        <v>45630</v>
+        <v>45627</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E45" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E45" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F45" s="3">
-        <v>427.5</v>
+        <v>0.33</v>
       </c>
       <c r="G45" s="9">
-        <v>275</v>
+        <v>235</v>
       </c>
       <c r="H45" s="6" t="str">
         <f>VLOOKUP(G45,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport_inc</v>
+        <v>InterestOnBankAccounts_inc</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>45</v>
       </c>
       <c r="B46" s="8">
         <v>45630</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D46" s="2">
-        <v>4245</v>
-      </c>
-      <c r="E46" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F46" s="3">
-        <v>750</v>
+        <v>427.5</v>
       </c>
       <c r="G46" s="9">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="H46" s="6" t="str">
         <f>VLOOKUP(G46,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>CasscadeMedicalFoundation</v>
+        <v>MiscCommunitySupport_inc</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>46</v>
       </c>
       <c r="B47" s="8">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2">
-        <v>4241</v>
-      </c>
-      <c r="E47" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4245</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F47" s="3">
-        <v>48.69</v>
+        <v>750</v>
       </c>
       <c r="G47" s="9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="H47" s="6" t="str">
         <f>VLOOKUP(G47,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Clothing4Kids</v>
+        <v>CasscadeMedicalFoundation</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>47</v>
       </c>
       <c r="B48" s="8">
         <v>45632</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D48" s="2">
-        <v>4244</v>
-      </c>
-      <c r="E48" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4241</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F48" s="3">
-        <v>1000</v>
+        <v>48.69</v>
       </c>
       <c r="G48" s="9">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="H48" s="6" t="str">
         <f>VLOOKUP(G48,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MEND</v>
+        <v>Clothing4Kids</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="B49" s="8">
         <v>45632</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D49" s="2">
-        <v>4246</v>
-      </c>
-      <c r="E49" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4244</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F49" s="3">
-        <v>96.12</v>
+        <v>1000</v>
       </c>
       <c r="G49" s="9">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="H49" s="6" t="str">
         <f>VLOOKUP(G49,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport</v>
+        <v>MEND</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>49</v>
       </c>
       <c r="B50" s="8">
-        <v>45635</v>
+        <v>45632</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="D50" s="2">
+        <v>4246</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F50" s="3">
-        <v>200</v>
+        <v>96.12</v>
       </c>
       <c r="G50" s="9">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H50" s="6" t="str">
         <f>VLOOKUP(G50,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport_inc</v>
+        <v>MiscCommunitySupport</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="B51" s="8">
         <v>45635</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E51" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F51" s="3">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="G51" s="9">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="H51" s="6" t="str">
         <f>VLOOKUP(G51,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Donations_inc</v>
+        <v>MiscCommunitySupport_inc</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>51</v>
       </c>
       <c r="B52" s="8">
-        <v>45637</v>
+        <v>45635</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D52" s="2">
-        <v>4247</v>
-      </c>
-      <c r="E52" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F52" s="3">
-        <v>25.34</v>
+        <v>140</v>
       </c>
       <c r="G52" s="9">
-        <v>310</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="str">
         <f>VLOOKUP(G52,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>SunshineCommittee</v>
+        <v>Donations_inc</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>52</v>
       </c>
       <c r="B53" s="8">
-        <v>45657</v>
+        <v>45637</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="D53" s="2">
+        <v>4247</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F53" s="3">
-        <v>0.3</v>
+        <v>25.34</v>
       </c>
       <c r="G53" s="9">
-        <v>235</v>
+        <v>310</v>
       </c>
       <c r="H53" s="6" t="str">
         <f>VLOOKUP(G53,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>InterestOnBankAccounts_inc</v>
+        <v>SunshineCommittee</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>53</v>
       </c>
       <c r="B54" s="8">
-        <v>45666</v>
+        <v>45657</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E54" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F54" s="3">
-        <v>3000</v>
+        <v>0.3</v>
       </c>
       <c r="G54" s="9">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="H54" s="6" t="str">
         <f>VLOOKUP(G54,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>AmbassadorChristmas_inc</v>
+        <v>InterestOnBankAccounts_inc</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>54</v>
       </c>
       <c r="B55" s="8">
@@ -2811,99 +2814,99 @@
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E55" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F55" s="3">
-        <v>5400</v>
+        <v>3000</v>
       </c>
       <c r="G55" s="9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H55" s="6" t="str">
         <f>VLOOKUP(G55,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>AmbassadorOctoberfest_inc</v>
+        <v>AmbassadorChristmas_inc</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="B56" s="8">
-        <v>45670</v>
+        <v>45666</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F56" s="3">
-        <v>130</v>
+        <v>5400</v>
       </c>
       <c r="G56" s="9">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="H56" s="6" t="str">
         <f>VLOOKUP(G56,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>ChamberCommerceDues</v>
+        <v>AmbassadorOctoberfest_inc</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="B57" s="8">
-        <v>45666</v>
+        <v>45670</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F57" s="3">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G57" s="9">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="H57" s="6" t="str">
         <f>VLOOKUP(G57,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Donations_inc</v>
+        <v>ChamberCommerceDues</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>57</v>
       </c>
       <c r="B58" s="8">
-        <v>45678</v>
+        <v>45666</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E58" s="2">
-        <f t="shared" si="2"/>
-        <v>1</v>
+      <c r="E58" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F58" s="3">
-        <v>394</v>
+        <v>148</v>
       </c>
       <c r="G58" s="9">
         <v>185</v>
@@ -2915,82 +2918,82 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>58</v>
       </c>
       <c r="B59" s="8">
-        <v>45679</v>
+        <v>45678</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" s="2">
-        <v>4251</v>
-      </c>
-      <c r="E59" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>21</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>DEP</v>
       </c>
       <c r="F59" s="3">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="G59" s="9">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="H59" s="6" t="str">
         <f>VLOOKUP(G59,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Health Permit</v>
+        <v>Donations_inc</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>59</v>
       </c>
       <c r="B60" s="8">
         <v>45679</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D60" s="2">
-        <v>4253</v>
-      </c>
-      <c r="E60" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4251</v>
+      </c>
+      <c r="E60" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F60" s="3">
-        <v>800</v>
+        <v>295</v>
       </c>
       <c r="G60" s="9">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="H60" s="6" t="str">
         <f>VLOOKUP(G60,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>ChestnutScoring</v>
+        <v>Health Permit</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="B61" s="8">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D61" s="2">
-        <v>4252</v>
-      </c>
-      <c r="E61" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4253</v>
+      </c>
+      <c r="E61" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F61" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G61" s="9">
         <v>140</v>
@@ -3002,256 +3005,256 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>61</v>
       </c>
       <c r="B62" s="8">
-        <v>45680</v>
+        <v>45678</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D62" s="2">
-        <v>4249</v>
-      </c>
-      <c r="E62" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4252</v>
+      </c>
+      <c r="E62" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F62" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="G62" s="9">
-        <v>260</v>
+        <v>140</v>
       </c>
       <c r="H62" s="6" t="str">
         <f>VLOOKUP(G62,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MEND</v>
+        <v>ChestnutScoring</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>62</v>
       </c>
       <c r="B63" s="8">
-        <v>45681</v>
+        <v>45680</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63" s="2">
-        <v>4248</v>
-      </c>
-      <c r="E63" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4249</v>
+      </c>
+      <c r="E63" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F63" s="3">
-        <v>39</v>
+        <v>500</v>
       </c>
       <c r="G63" s="9">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="H63" s="6" t="str">
         <f>VLOOKUP(G63,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>EyeGlasses &amp; HearingAids</v>
+        <v>MEND</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="B64" s="8">
-        <v>45684</v>
+        <v>45681</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D64" s="2">
-        <v>4254</v>
-      </c>
-      <c r="E64" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4248</v>
+      </c>
+      <c r="E64" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F64" s="3">
-        <v>1000</v>
+        <v>39</v>
       </c>
       <c r="G64" s="9">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="H64" s="6" t="str">
         <f>VLOOKUP(G64,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>LCIF</v>
+        <v>EyeGlasses &amp; HearingAids</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="B65" s="8">
-        <v>45688</v>
+        <v>45684</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" s="2">
-        <v>4255</v>
-      </c>
-      <c r="E65" s="2">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4254</v>
+      </c>
+      <c r="E65" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F65" s="3">
-        <v>255</v>
+        <v>1000</v>
       </c>
       <c r="G65" s="9">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="H65" s="6" t="str">
         <f>VLOOKUP(G65,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>PublicRelations</v>
+        <v>LCIF</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>65</v>
       </c>
       <c r="B66" s="8">
-        <v>45686</v>
+        <v>45688</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D66" s="2">
-        <v>4250</v>
-      </c>
-      <c r="E66" s="2">
-        <f t="shared" ref="E66:E83" si="4">IF(D66=$J$1, 1, 0)</f>
-        <v>0</v>
+        <v>4255</v>
+      </c>
+      <c r="E66" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>EXP</v>
       </c>
       <c r="F66" s="3">
-        <v>119.8</v>
+        <v>255</v>
       </c>
       <c r="G66" s="9">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="H66" s="6" t="str">
         <f>VLOOKUP(G66,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport</v>
+        <v>PublicRelations</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
-        <f t="shared" ref="A67:A85" si="5">A66+1</f>
+        <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="B67" s="8">
-        <v>45690</v>
+        <v>45686</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="D67" s="2">
+        <v>4250</v>
+      </c>
+      <c r="E67" s="2" t="str">
+        <f t="shared" ref="E67:E86" si="3">IF(D67=$J$1, "DEP","EXP")</f>
+        <v>EXP</v>
       </c>
       <c r="F67" s="3">
-        <v>0.38</v>
+        <v>119.8</v>
       </c>
       <c r="G67" s="9">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="H67" s="6" t="str">
         <f>VLOOKUP(G67,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>InterestOnBankAccounts_inc</v>
+        <v>MiscCommunitySupport</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A68:A86" si="4">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68" s="8">
-        <v>45695</v>
+        <v>45690</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="2">
-        <f t="shared" si="4"/>
-        <v>1</v>
+      <c r="E68" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>DEP</v>
       </c>
       <c r="F68" s="3">
-        <v>3000</v>
+        <v>0.38</v>
       </c>
       <c r="G68" s="9">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="H68" s="6" t="str">
         <f>VLOOKUP(G68,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>ChestnutScoring_inc</v>
+        <v>InterestOnBankAccounts_inc</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>68</v>
       </c>
       <c r="B69" s="8">
         <v>45695</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="2">
-        <v>4256</v>
-      </c>
-      <c r="E69" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>DEP</v>
       </c>
       <c r="F69" s="3">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="G69" s="9">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H69" s="6" t="str">
         <f>VLOOKUP(G69,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>ChestnutScoring</v>
+        <v>ChestnutScoring_inc</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>69</v>
       </c>
       <c r="B70" s="8">
         <v>45695</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D70" s="2">
-        <v>4257</v>
-      </c>
-      <c r="E70" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4256</v>
+      </c>
+      <c r="E70" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F70" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G70" s="9">
         <v>140</v>
@@ -3263,113 +3266,113 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>70</v>
       </c>
       <c r="B71" s="8">
         <v>45695</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D71" s="2">
-        <v>4259</v>
-      </c>
-      <c r="E71" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4257</v>
+      </c>
+      <c r="E71" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F71" s="3">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="G71" s="9">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="H71" s="6" t="str">
         <f>VLOOKUP(G71,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>CampStix</v>
+        <v>ChestnutScoring</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="B72" s="8">
-        <v>45699</v>
+        <v>45695</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D72" s="2">
-        <v>4258</v>
-      </c>
-      <c r="E72" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4259</v>
+      </c>
+      <c r="E72" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F72" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="G72" s="9">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H72" s="6" t="str">
         <f>VLOOKUP(G72,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>YouthSports</v>
+        <v>CampStix</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>72</v>
       </c>
       <c r="B73" s="8">
-        <v>45709</v>
+        <v>45699</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" s="2">
-        <v>4260</v>
-      </c>
-      <c r="E73" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4258</v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F73" s="3">
-        <v>338.94</v>
+        <v>500</v>
       </c>
       <c r="G73" s="9">
-        <v>270</v>
+        <v>350</v>
       </c>
       <c r="H73" s="6" t="str">
         <f>VLOOKUP(G73,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MiscCommunitySupport</v>
+        <v>YouthSports</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>73</v>
       </c>
       <c r="B74" s="8">
         <v>45709</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="4">
-        <v>4261</v>
-      </c>
-      <c r="E74" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="D74" s="2">
+        <v>4260</v>
+      </c>
+      <c r="E74" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F74" s="3">
-        <v>250</v>
-      </c>
-      <c r="G74" s="2">
+        <v>338.94</v>
+      </c>
+      <c r="G74" s="9">
         <v>270</v>
       </c>
       <c r="H74" s="6" t="str">
@@ -3379,297 +3382,297 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>74</v>
       </c>
       <c r="B75" s="8">
         <v>45709</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D75" s="4">
-        <v>4262</v>
-      </c>
-      <c r="E75" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4261</v>
+      </c>
+      <c r="E75" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F75" s="3">
-        <v>68.42</v>
+        <v>250</v>
       </c>
       <c r="G75" s="2">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="H75" s="6" t="str">
         <f>VLOOKUP(G75,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>PublicRelations</v>
+        <v>MiscCommunitySupport</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>75</v>
       </c>
       <c r="B76" s="8">
-        <v>45714</v>
+        <v>45709</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76" s="4">
-        <v>4263</v>
-      </c>
-      <c r="E76" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4262</v>
+      </c>
+      <c r="E76" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F76" s="3">
-        <v>200</v>
+        <v>68.42</v>
       </c>
       <c r="G76" s="2">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="H76" s="6" t="str">
         <f>VLOOKUP(G76,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>LeavenworthActivityFee</v>
+        <v>PublicRelations</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="B77" s="8">
-        <v>45724</v>
+        <v>45714</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D77" s="4">
-        <v>4264</v>
-      </c>
-      <c r="E77" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4263</v>
+      </c>
+      <c r="E77" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F77" s="3">
-        <v>1500</v>
+        <v>200</v>
       </c>
       <c r="G77" s="2">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="H77" s="6" t="str">
         <f>VLOOKUP(G77,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>BackPackProgram</v>
+        <v>LeavenworthActivityFee</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="B78" s="8">
-        <v>45731</v>
+        <v>45724</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" s="4">
-        <v>4265</v>
-      </c>
-      <c r="E78" s="2">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4264</v>
+      </c>
+      <c r="E78" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F78" s="3">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="G78" s="2">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="H78" s="6" t="str">
         <f>VLOOKUP(G78,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>CasscadeMedicalFoundation</v>
+        <v>BackPackProgram</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>78</v>
       </c>
       <c r="B79" s="8">
-        <v>45752</v>
+        <v>45731</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79" s="4">
-        <v>4266</v>
-      </c>
-      <c r="E79" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4265</v>
+      </c>
+      <c r="E79" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F79" s="3">
-        <v>500</v>
+        <v>1100</v>
       </c>
       <c r="G79" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="H79" s="6" t="str">
         <f>VLOOKUP(G79,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>CAREMD19</v>
+        <v>CasscadeMedicalFoundation</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>79</v>
       </c>
       <c r="B80" s="8">
         <v>45752</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" s="4">
-        <v>4267</v>
-      </c>
-      <c r="E80" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4266</v>
+      </c>
+      <c r="E80" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F80" s="3">
-        <v>119.29</v>
+        <v>500</v>
       </c>
       <c r="G80" s="2">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="H80" s="6" t="str">
         <f>VLOOKUP(G80,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>EasterEggHunt</v>
+        <v>CAREMD19</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="B81" s="8">
-        <v>45763</v>
+        <v>45752</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D81" s="4">
-        <v>4268</v>
-      </c>
-      <c r="E81" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4267</v>
+      </c>
+      <c r="E81" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F81" s="3">
-        <v>126.94</v>
+        <v>119.29</v>
       </c>
       <c r="G81" s="2">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="H81" s="6" t="str">
         <f>VLOOKUP(G81,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>Breakfast May-June 2025</v>
+        <v>EasterEggHunt</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>81</v>
       </c>
       <c r="B82" s="8">
-        <v>45764</v>
+        <v>45763</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D82" s="4">
-        <v>4269</v>
-      </c>
-      <c r="E82" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4268</v>
+      </c>
+      <c r="E82" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F82" s="3">
-        <v>200</v>
+        <v>126.94</v>
       </c>
       <c r="G82" s="2">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="H82" s="6" t="str">
         <f>VLOOKUP(G82,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>MEND</v>
+        <v>Breakfast May-June 2025</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>82</v>
       </c>
       <c r="B83" s="8">
-        <v>45765</v>
+        <v>45764</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E83" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="D83" s="4">
+        <v>4269</v>
+      </c>
+      <c r="E83" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F83" s="3">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="G83" s="2">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="H83" s="6" t="str">
         <f>VLOOKUP(G83,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>EasterEggHunt</v>
+        <v>MEND</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>83</v>
       </c>
       <c r="B84" s="8">
-        <v>45769</v>
+        <v>45765</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="2">
-        <f>IF(D84=$J$1,0,1)</f>
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="E84" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>EXP</v>
       </c>
       <c r="F84" s="3">
-        <v>22.25</v>
+        <v>60</v>
       </c>
       <c r="G84" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H84" s="6" t="str">
         <f>VLOOKUP(G84,[1]Resources!$A$2:$B$84,2,FALSE)</f>
-        <v>EasterEggHunt_inc</v>
+        <v>EasterEggHunt</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="B85" s="8">
@@ -3681,18 +3684,47 @@
       <c r="D85" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="2">
-        <f>IF(D85=$J$1,0,1)</f>
-        <v>0</v>
+      <c r="E85" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>DEP</v>
       </c>
       <c r="F85" s="3">
-        <v>21</v>
+        <v>22.25</v>
       </c>
       <c r="G85" s="2">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="H85" s="6" t="str">
         <f>VLOOKUP(G85,[1]Resources!$A$2:$B$84,2,FALSE)</f>
+        <v>EasterEggHunt_inc</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <f t="shared" si="4"/>
+        <v>85</v>
+      </c>
+      <c r="B86" s="8">
+        <v>45769</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v>DEP</v>
+      </c>
+      <c r="F86" s="3">
+        <v>21</v>
+      </c>
+      <c r="G86" s="2">
+        <v>185</v>
+      </c>
+      <c r="H86" s="6" t="str">
+        <f>VLOOKUP(G86,[1]Resources!$A$2:$B$84,2,FALSE)</f>
         <v>Donations_inc</v>
       </c>
     </row>
